--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/20.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/20.xlsx
@@ -426,13 +426,13 @@
         <v>-20.82663323936601</v>
       </c>
       <c r="E2">
-        <v>-35.32264048918031</v>
+        <v>-33.08634190573545</v>
       </c>
       <c r="F2">
-        <v>-5.800005235437302</v>
+        <v>-5.347041588032889</v>
       </c>
       <c r="G2">
-        <v>-23.63231227475524</v>
+        <v>-19.01324381617726</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.63475411633016</v>
       </c>
       <c r="E3">
-        <v>-35.18650323932471</v>
+        <v>-33.37872283004069</v>
       </c>
       <c r="F3">
-        <v>-5.693210402588516</v>
+        <v>-4.628553806845898</v>
       </c>
       <c r="G3">
-        <v>-23.51191600985579</v>
+        <v>-20.52322170791255</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.3583936463179</v>
       </c>
       <c r="E4">
-        <v>-35.80360971353497</v>
+        <v>-35.03843346045892</v>
       </c>
       <c r="F4">
-        <v>-5.558243817062936</v>
+        <v>-5.34577383144758</v>
       </c>
       <c r="G4">
-        <v>-23.27135025242634</v>
+        <v>-19.74947769392855</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.99792789923798</v>
       </c>
       <c r="E5">
-        <v>-36.83202389643991</v>
+        <v>-33.79180343630937</v>
       </c>
       <c r="F5">
-        <v>-5.752011027669909</v>
+        <v>-4.667980165610762</v>
       </c>
       <c r="G5">
-        <v>-23.70916824472219</v>
+        <v>-19.77637256588959</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.56010877064244</v>
       </c>
       <c r="E6">
-        <v>-36.50397218237625</v>
+        <v>-34.3638470656693</v>
       </c>
       <c r="F6">
-        <v>-5.582474517569159</v>
+        <v>-5.259224303168813</v>
       </c>
       <c r="G6">
-        <v>-23.33047162993942</v>
+        <v>-19.9708108370476</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.05298841608668</v>
       </c>
       <c r="E7">
-        <v>-37.26567283165143</v>
+        <v>-34.33951104635208</v>
       </c>
       <c r="F7">
-        <v>-5.513474826392335</v>
+        <v>-5.175397165358688</v>
       </c>
       <c r="G7">
-        <v>-23.03800976063635</v>
+        <v>-18.93751012114812</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.48782935326205</v>
       </c>
       <c r="E8">
-        <v>-36.51773195064856</v>
+        <v>-35.3303139883863</v>
       </c>
       <c r="F8">
-        <v>-5.759258857791918</v>
+        <v>-4.729598203515723</v>
       </c>
       <c r="G8">
-        <v>-23.06493608278002</v>
+        <v>-19.53179773781208</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.87953267913186</v>
       </c>
       <c r="E9">
-        <v>-37.26987072705654</v>
+        <v>-34.77642274708612</v>
       </c>
       <c r="F9">
-        <v>-5.529025234776036</v>
+        <v>-4.730638698302166</v>
       </c>
       <c r="G9">
-        <v>-22.61535903272868</v>
+        <v>-20.03413495212278</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.24205417900368</v>
       </c>
       <c r="E10">
-        <v>-37.84764740451018</v>
+        <v>-35.88513130262105</v>
       </c>
       <c r="F10">
-        <v>-5.587830610975176</v>
+        <v>-4.686966423978008</v>
       </c>
       <c r="G10">
-        <v>-22.34668674367082</v>
+        <v>-17.49267714453461</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.59846362770834</v>
       </c>
       <c r="E11">
-        <v>-38.48398857206801</v>
+        <v>-36.13787675817416</v>
       </c>
       <c r="F11">
-        <v>-5.299602469188858</v>
+        <v>-4.798452193748326</v>
       </c>
       <c r="G11">
-        <v>-22.20129917049541</v>
+        <v>-18.58502806121807</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.96834001264173</v>
       </c>
       <c r="E12">
-        <v>-38.08299219868881</v>
+        <v>-36.72909168224556</v>
       </c>
       <c r="F12">
-        <v>-5.123404100154811</v>
+        <v>-4.660957221728746</v>
       </c>
       <c r="G12">
-        <v>-21.4887092089856</v>
+        <v>-18.63383377883078</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.36378906583854</v>
       </c>
       <c r="E13">
-        <v>-39.5258953432788</v>
+        <v>-37.33513283021808</v>
       </c>
       <c r="F13">
-        <v>-5.331729527389462</v>
+        <v>-4.879692347945581</v>
       </c>
       <c r="G13">
-        <v>-21.68268400376812</v>
+        <v>-18.12354132358921</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.80904918773032</v>
       </c>
       <c r="E14">
-        <v>-40.16608118526916</v>
+        <v>-37.01489273381765</v>
       </c>
       <c r="F14">
-        <v>-5.477195291281449</v>
+        <v>-5.008980555911354</v>
       </c>
       <c r="G14">
-        <v>-21.24844967701853</v>
+        <v>-18.53665271452547</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.31623693850413</v>
       </c>
       <c r="E15">
-        <v>-40.52990105128239</v>
+        <v>-38.19089214886957</v>
       </c>
       <c r="F15">
-        <v>-5.262291149674062</v>
+        <v>-5.056024540129482</v>
       </c>
       <c r="G15">
-        <v>-20.53891203849593</v>
+        <v>-17.0469635011276</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.89303306592052</v>
       </c>
       <c r="E16">
-        <v>-40.4356204866797</v>
+        <v>-39.21472578031575</v>
       </c>
       <c r="F16">
-        <v>-5.399225489799576</v>
+        <v>-4.42971398619177</v>
       </c>
       <c r="G16">
-        <v>-20.04385140328054</v>
+        <v>-17.54674828482753</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.5427234219325</v>
       </c>
       <c r="E17">
-        <v>-41.1054723618943</v>
+        <v>-39.67421645245204</v>
       </c>
       <c r="F17">
-        <v>-5.195668601076314</v>
+        <v>-4.375643098826837</v>
       </c>
       <c r="G17">
-        <v>-20.08300191482796</v>
+        <v>-17.71818323030591</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.26055788367027</v>
       </c>
       <c r="E18">
-        <v>-41.25867969452181</v>
+        <v>-39.23513561266832</v>
       </c>
       <c r="F18">
-        <v>-4.857050104472543</v>
+        <v>-4.401788499784827</v>
       </c>
       <c r="G18">
-        <v>-20.2466554230163</v>
+        <v>-16.75971077523058</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.04291285047643</v>
       </c>
       <c r="E19">
-        <v>-42.10398503092659</v>
+        <v>-38.91152406736918</v>
       </c>
       <c r="F19">
-        <v>-4.846371175484735</v>
+        <v>-4.398895069077319</v>
       </c>
       <c r="G19">
-        <v>-19.41830064981648</v>
+        <v>-16.06046231224403</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.88267532059013</v>
       </c>
       <c r="E20">
-        <v>-42.28767125786272</v>
+        <v>-40.33477589900289</v>
       </c>
       <c r="F20">
-        <v>-4.723953875633097</v>
+        <v>-3.879636700199653</v>
       </c>
       <c r="G20">
-        <v>-19.24872126511285</v>
+        <v>-15.71114678912229</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.76631023375431</v>
       </c>
       <c r="E21">
-        <v>-42.84231875432219</v>
+        <v>-41.81221092213838</v>
       </c>
       <c r="F21">
-        <v>-5.062124975315755</v>
+        <v>-3.972654083437073</v>
       </c>
       <c r="G21">
-        <v>-19.83578858195566</v>
+        <v>-15.18920121358249</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.68500239700296</v>
       </c>
       <c r="E22">
-        <v>-43.06544572562812</v>
+        <v>-39.64377152169847</v>
       </c>
       <c r="F22">
-        <v>-4.705191711652885</v>
+        <v>-3.438051979797671</v>
       </c>
       <c r="G22">
-        <v>-18.94480987406222</v>
+        <v>-15.23969034360191</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.63003413319817</v>
       </c>
       <c r="E23">
-        <v>-42.80257913066787</v>
+        <v>-40.77636324914985</v>
       </c>
       <c r="F23">
-        <v>-4.579212657197424</v>
+        <v>-3.738187214509221</v>
       </c>
       <c r="G23">
-        <v>-18.93918194664545</v>
+        <v>-15.5524408912424</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.59067707358617</v>
       </c>
       <c r="E24">
-        <v>-43.96463311001317</v>
+        <v>-41.98427482053383</v>
       </c>
       <c r="F24">
-        <v>-4.567279433124588</v>
+        <v>-3.529159413701072</v>
       </c>
       <c r="G24">
-        <v>-19.13381222944475</v>
+        <v>-15.12370207008801</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.55782885549856</v>
       </c>
       <c r="E25">
-        <v>-44.26807256784514</v>
+        <v>-41.0822095909169</v>
       </c>
       <c r="F25">
-        <v>-4.321285560691209</v>
+        <v>-3.346581877239635</v>
       </c>
       <c r="G25">
-        <v>-18.72797245178549</v>
+        <v>-15.40714766861487</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.52265266988181</v>
       </c>
       <c r="E26">
-        <v>-44.12935408780518</v>
+        <v>-43.1401791321767</v>
       </c>
       <c r="F26">
-        <v>-4.219828608630412</v>
+        <v>-4.188377792855699</v>
       </c>
       <c r="G26">
-        <v>-18.79897372196624</v>
+        <v>-15.50634319988082</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.47754397655455</v>
       </c>
       <c r="E27">
-        <v>-44.77963389835862</v>
+        <v>-41.93740737879144</v>
       </c>
       <c r="F27">
-        <v>-4.324947088767705</v>
+        <v>-3.901279625240048</v>
       </c>
       <c r="G27">
-        <v>-18.63044543547133</v>
+        <v>-15.2880938299316</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.4215251935921</v>
       </c>
       <c r="E28">
-        <v>-44.06306402104389</v>
+        <v>-42.47443005441306</v>
       </c>
       <c r="F28">
-        <v>-4.28346824713643</v>
+        <v>-3.35941147886061</v>
       </c>
       <c r="G28">
-        <v>-18.9430387321987</v>
+        <v>-15.54781936966958</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.3521727900761</v>
       </c>
       <c r="E29">
-        <v>-44.1477283710913</v>
+        <v>-41.21531502742435</v>
       </c>
       <c r="F29">
-        <v>-4.453935184462502</v>
+        <v>-3.519794168770121</v>
       </c>
       <c r="G29">
-        <v>-18.98266265175824</v>
+        <v>-14.95844956840421</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.26722749473814</v>
       </c>
       <c r="E30">
-        <v>-44.08088356626407</v>
+        <v>-41.87165620043707</v>
       </c>
       <c r="F30">
-        <v>-4.467217725975292</v>
+        <v>-3.693727838345089</v>
       </c>
       <c r="G30">
-        <v>-18.92210615275389</v>
+        <v>-15.37505855070271</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.17223922072596</v>
       </c>
       <c r="E31">
-        <v>-43.76977740193712</v>
+        <v>-42.37594706593124</v>
       </c>
       <c r="F31">
-        <v>-4.485801723040017</v>
+        <v>-3.600464980690775</v>
       </c>
       <c r="G31">
-        <v>-18.99194045563205</v>
+        <v>-15.45026917953664</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.06934090677841</v>
       </c>
       <c r="E32">
-        <v>-44.48898737959832</v>
+        <v>-41.55021379418761</v>
       </c>
       <c r="F32">
-        <v>-4.501674415577508</v>
+        <v>-3.604082165001639</v>
       </c>
       <c r="G32">
-        <v>-18.9260688757644</v>
+        <v>-16.05037839053141</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.96111953809497</v>
       </c>
       <c r="E33">
-        <v>-44.15690079519383</v>
+        <v>-40.76577114844591</v>
       </c>
       <c r="F33">
-        <v>-4.614393100402996</v>
+        <v>-3.556936823604922</v>
       </c>
       <c r="G33">
-        <v>-18.5915680439309</v>
+        <v>-16.63422289129174</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.85044880863285</v>
       </c>
       <c r="E34">
-        <v>-43.24622693648833</v>
+        <v>-39.9308337532817</v>
       </c>
       <c r="F34">
-        <v>-4.460602586366502</v>
+        <v>-3.433360251023182</v>
       </c>
       <c r="G34">
-        <v>-19.14704447996521</v>
+        <v>-16.76367349824109</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.73620548625948</v>
       </c>
       <c r="E35">
-        <v>-42.87050397654593</v>
+        <v>-39.88873479466938</v>
       </c>
       <c r="F35">
-        <v>-4.252814035437185</v>
+        <v>-3.550227453494163</v>
       </c>
       <c r="G35">
-        <v>-19.09004681741558</v>
+        <v>-15.94600682131481</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.62385158621619</v>
       </c>
       <c r="E36">
-        <v>-43.03382792010657</v>
+        <v>-40.90936679499214</v>
       </c>
       <c r="F36">
-        <v>-4.350474844418674</v>
+        <v>-3.735828284548174</v>
       </c>
       <c r="G36">
-        <v>-19.66273146916302</v>
+        <v>-16.09100871593489</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.51615186560503</v>
       </c>
       <c r="E37">
-        <v>-43.31150262507189</v>
+        <v>-40.41295547427131</v>
       </c>
       <c r="F37">
-        <v>-4.293200911839763</v>
+        <v>-3.340477482788574</v>
       </c>
       <c r="G37">
-        <v>-18.92881331801646</v>
+        <v>-15.88882707876052</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.4121166259814</v>
       </c>
       <c r="E38">
-        <v>-42.22894147845724</v>
+        <v>-39.66696183709175</v>
       </c>
       <c r="F38">
-        <v>-4.394687162459997</v>
+        <v>-3.164748682558455</v>
       </c>
       <c r="G38">
-        <v>-19.56913572567675</v>
+        <v>-16.50199804718048</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.31632192930989</v>
       </c>
       <c r="E39">
-        <v>-42.02916558337186</v>
+        <v>-40.25771485681437</v>
       </c>
       <c r="F39">
-        <v>-4.038008875449512</v>
+        <v>-3.521314526448942</v>
       </c>
       <c r="G39">
-        <v>-19.52804192389778</v>
+        <v>-16.56011632939515</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.23059112223875</v>
       </c>
       <c r="E40">
-        <v>-41.6597236168781</v>
+        <v>-38.56553053928713</v>
       </c>
       <c r="F40">
-        <v>-4.456698751284944</v>
+        <v>-3.378919568326993</v>
       </c>
       <c r="G40">
-        <v>-19.38399346639301</v>
+        <v>-16.197783741213</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.15490900209225</v>
       </c>
       <c r="E41">
-        <v>-41.84090559768799</v>
+        <v>-37.8523841883222</v>
       </c>
       <c r="F41">
-        <v>-4.293110640602584</v>
+        <v>-3.279295755863317</v>
       </c>
       <c r="G41">
-        <v>-19.6862611715834</v>
+        <v>-16.1458214184286</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.08880867270751</v>
       </c>
       <c r="E42">
-        <v>-41.20864458521105</v>
+        <v>-37.5446109808649</v>
       </c>
       <c r="F42">
-        <v>-4.03085606768243</v>
+        <v>-3.237499381195997</v>
       </c>
       <c r="G42">
-        <v>-19.10905928044762</v>
+        <v>-17.02929677485728</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.02929144892835</v>
       </c>
       <c r="E43">
-        <v>-41.65091799917018</v>
+        <v>-37.65434949149277</v>
       </c>
       <c r="F43">
-        <v>-3.898284837353952</v>
+        <v>-3.258780429434715</v>
       </c>
       <c r="G43">
-        <v>-19.15662188821032</v>
+        <v>-16.57968992989609</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.97475313176096</v>
       </c>
       <c r="E44">
-        <v>-40.64126754831603</v>
+        <v>-37.90722174431809</v>
       </c>
       <c r="F44">
-        <v>-4.232719974782089</v>
+        <v>-3.405150489404417</v>
       </c>
       <c r="G44">
-        <v>-19.68742813888599</v>
+        <v>-17.45449827810296</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.92640983332303</v>
       </c>
       <c r="E45">
-        <v>-40.25652613238735</v>
+        <v>-36.92749318546961</v>
       </c>
       <c r="F45">
-        <v>-4.07710107226622</v>
+        <v>-3.35393185639319</v>
       </c>
       <c r="G45">
-        <v>-19.7235643987199</v>
+        <v>-17.48810859169042</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.88274929883455</v>
       </c>
       <c r="E46">
-        <v>-40.66632812347448</v>
+        <v>-36.28223998106468</v>
       </c>
       <c r="F46">
-        <v>-4.03051240349878</v>
+        <v>-3.318370531914955</v>
       </c>
       <c r="G46">
-        <v>-19.76006647383591</v>
+        <v>-17.1946899747265</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.84345406665342</v>
       </c>
       <c r="E47">
-        <v>-39.09976820339403</v>
+        <v>-36.60133663777817</v>
       </c>
       <c r="F47">
-        <v>-4.059708813902864</v>
+        <v>-3.322293371467498</v>
       </c>
       <c r="G47">
-        <v>-20.04647004480211</v>
+        <v>-17.61151579775783</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.81168209191291</v>
       </c>
       <c r="E48">
-        <v>-39.7195396845578</v>
+        <v>-35.80926351333355</v>
       </c>
       <c r="F48">
-        <v>-4.005491433740752</v>
+        <v>-2.98398686492907</v>
       </c>
       <c r="G48">
-        <v>-19.71780404948157</v>
+        <v>-17.43582680126148</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.78756286918916</v>
       </c>
       <c r="E49">
-        <v>-38.66993450753397</v>
+        <v>-35.73967898173169</v>
       </c>
       <c r="F49">
-        <v>-3.885218471698619</v>
+        <v>-2.941623523544022</v>
       </c>
       <c r="G49">
-        <v>-20.00745195507626</v>
+        <v>-17.07887550485341</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.77096108142115</v>
       </c>
       <c r="E50">
-        <v>-38.45452632017412</v>
+        <v>-34.08095329441013</v>
       </c>
       <c r="F50">
-        <v>-3.965093471396765</v>
+        <v>-3.351373379486797</v>
       </c>
       <c r="G50">
-        <v>-19.77145143994546</v>
+        <v>-17.38756897893552</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.76123698770293</v>
       </c>
       <c r="E51">
-        <v>-38.44259831963791</v>
+        <v>-34.72112328674145</v>
       </c>
       <c r="F51">
-        <v>-3.787235378563338</v>
+        <v>-3.033983668826535</v>
       </c>
       <c r="G51">
-        <v>-20.18441882215077</v>
+        <v>-16.93812435070576</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.75419619492511</v>
       </c>
       <c r="E52">
-        <v>-38.33577161779696</v>
+        <v>-34.7970748527981</v>
       </c>
       <c r="F52">
-        <v>-3.744536291524217</v>
+        <v>-3.101961869687901</v>
       </c>
       <c r="G52">
-        <v>-20.21779243173216</v>
+        <v>-17.52379792787653</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.75252192900929</v>
       </c>
       <c r="E53">
-        <v>-37.77934443105249</v>
+        <v>-34.08266958605903</v>
       </c>
       <c r="F53">
-        <v>-4.221963444204424</v>
+        <v>-2.863674310239051</v>
       </c>
       <c r="G53">
-        <v>-20.62683516220066</v>
+        <v>-17.06193047751065</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.75616788177061</v>
       </c>
       <c r="E54">
-        <v>-38.05343258460374</v>
+        <v>-33.20327389732451</v>
       </c>
       <c r="F54">
-        <v>-3.842854338460614</v>
+        <v>-3.020424770631501</v>
       </c>
       <c r="G54">
-        <v>-20.17966984457468</v>
+        <v>-17.18361785517041</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.76211432884396</v>
       </c>
       <c r="E55">
-        <v>-37.40219953027167</v>
+        <v>-32.10858096884331</v>
       </c>
       <c r="F55">
-        <v>-3.82483968367249</v>
+        <v>-3.589860485880993</v>
       </c>
       <c r="G55">
-        <v>-20.36467968203685</v>
+        <v>-17.49939258616102</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.7743356057615</v>
       </c>
       <c r="E56">
-        <v>-36.95839549209796</v>
+        <v>-32.89513161923558</v>
       </c>
       <c r="F56">
-        <v>-4.141182564722646</v>
+        <v>-2.97058950473741</v>
       </c>
       <c r="G56">
-        <v>-20.36152969795624</v>
+        <v>-17.51499518728761</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.79321281258669</v>
       </c>
       <c r="E57">
-        <v>-36.66048530102935</v>
+        <v>-32.51832635400534</v>
       </c>
       <c r="F57">
-        <v>-4.114687164757345</v>
+        <v>-3.411443344859415</v>
       </c>
       <c r="G57">
-        <v>-20.58698281499891</v>
+        <v>-17.86695252574969</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.81857045186774</v>
       </c>
       <c r="E58">
-        <v>-36.27819378953883</v>
+        <v>-32.39175776972796</v>
       </c>
       <c r="F58">
-        <v>-4.254513351884451</v>
+        <v>-3.211764951923064</v>
       </c>
       <c r="G58">
-        <v>-20.85514196949819</v>
+        <v>-16.93578213973672</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.85005524116868</v>
       </c>
       <c r="E59">
-        <v>-36.20457665183314</v>
+        <v>-32.40526394345584</v>
       </c>
       <c r="F59">
-        <v>-4.090728861668577</v>
+        <v>-3.64835783127958</v>
       </c>
       <c r="G59">
-        <v>-20.74493721904139</v>
+        <v>-17.12320867544256</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.88425868960048</v>
       </c>
       <c r="E60">
-        <v>-36.16319772058804</v>
+        <v>-30.81428649152603</v>
       </c>
       <c r="F60">
-        <v>-4.296551241703876</v>
+        <v>-3.697650677897633</v>
       </c>
       <c r="G60">
-        <v>-20.55700251459527</v>
+        <v>-18.24863856315442</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.92120830674617</v>
       </c>
       <c r="E61">
-        <v>-35.52708524096759</v>
+        <v>-31.13179365386283</v>
       </c>
       <c r="F61">
-        <v>-4.151988190183689</v>
+        <v>-3.648806811906607</v>
       </c>
       <c r="G61">
-        <v>-20.62605221818062</v>
+        <v>-17.22209467070059</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.96197368196855</v>
       </c>
       <c r="E62">
-        <v>-35.97134212654208</v>
+        <v>-30.39156929256903</v>
       </c>
       <c r="F62">
-        <v>-4.406790634918742</v>
+        <v>-3.82749635034564</v>
       </c>
       <c r="G62">
-        <v>-20.64589397287024</v>
+        <v>-17.89040111980434</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.00470608362858</v>
       </c>
       <c r="E63">
-        <v>-34.23199148798796</v>
+        <v>-31.22523192230009</v>
       </c>
       <c r="F63">
-        <v>-4.459230305190774</v>
+        <v>-3.746121581145572</v>
       </c>
       <c r="G63">
-        <v>-20.73194829361806</v>
+        <v>-18.22555412910908</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.05048263143494</v>
       </c>
       <c r="E64">
-        <v>-35.05726964809382</v>
+        <v>-31.08215025755374</v>
       </c>
       <c r="F64">
-        <v>-4.219100895762267</v>
+        <v>-3.776081337800898</v>
       </c>
       <c r="G64">
-        <v>-21.01245909352436</v>
+        <v>-18.44167647354932</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.10177831173823</v>
       </c>
       <c r="E65">
-        <v>-34.85184901015788</v>
+        <v>-30.92944332130408</v>
       </c>
       <c r="F65">
-        <v>-4.43459655152907</v>
+        <v>-3.522818255215652</v>
       </c>
       <c r="G65">
-        <v>-20.32588174358936</v>
+        <v>-17.98659564153894</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.15910052326339</v>
       </c>
       <c r="E66">
-        <v>-35.16767610863783</v>
+        <v>-30.66463853946856</v>
       </c>
       <c r="F66">
-        <v>-4.450514379685153</v>
+        <v>-3.637987724945282</v>
       </c>
       <c r="G66">
-        <v>-20.62480910833062</v>
+        <v>-17.42055856523436</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.22283338067048</v>
       </c>
       <c r="E67">
-        <v>-34.56190666910577</v>
+        <v>-31.2471384153122</v>
       </c>
       <c r="F67">
-        <v>-4.306221350023549</v>
+        <v>-3.99425820768254</v>
       </c>
       <c r="G67">
-        <v>-21.08812326709717</v>
+        <v>-18.25698444845892</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.29213948156508</v>
       </c>
       <c r="E68">
-        <v>-35.0658782771824</v>
+        <v>-30.2294340734354</v>
       </c>
       <c r="F68">
-        <v>-4.388219307501342</v>
+        <v>-4.148947474826046</v>
       </c>
       <c r="G68">
-        <v>-20.95687834446553</v>
+        <v>-17.32616663554589</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.36416676080438</v>
       </c>
       <c r="E69">
-        <v>-34.11812300906509</v>
+        <v>-29.4648238796103</v>
       </c>
       <c r="F69">
-        <v>-4.338528950698514</v>
+        <v>-4.513522119530911</v>
       </c>
       <c r="G69">
-        <v>-21.47934698620054</v>
+        <v>-17.80302258084082</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.44189587960535</v>
       </c>
       <c r="E70">
-        <v>-35.67277077826836</v>
+        <v>-30.98953617138587</v>
       </c>
       <c r="F70">
-        <v>-4.409434631944569</v>
+        <v>-4.013717994118503</v>
       </c>
       <c r="G70">
-        <v>-20.868845972758</v>
+        <v>-18.46619933963147</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.52490655905634</v>
       </c>
       <c r="E71">
-        <v>-34.88605710281182</v>
+        <v>-31.07953732805131</v>
       </c>
       <c r="F71">
-        <v>-4.624962753682638</v>
+        <v>-4.205733625983001</v>
       </c>
       <c r="G71">
-        <v>-20.40063386186611</v>
+        <v>-17.4790658365499</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.61047106293668</v>
       </c>
       <c r="E72">
-        <v>-34.63427621222235</v>
+        <v>-29.45280078111994</v>
       </c>
       <c r="F72">
-        <v>-4.623553255417898</v>
+        <v>-4.411182251422256</v>
       </c>
       <c r="G72">
-        <v>-20.43324108015516</v>
+        <v>-17.56462854128513</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.70185911890994</v>
       </c>
       <c r="E73">
-        <v>-34.34652338835296</v>
+        <v>-30.94634585053771</v>
       </c>
       <c r="F73">
-        <v>-4.68291688795223</v>
+        <v>-4.153316919446744</v>
       </c>
       <c r="G73">
-        <v>-21.04146774881222</v>
+        <v>-17.56718924825976</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.7975457397224</v>
       </c>
       <c r="E74">
-        <v>-35.55116540150338</v>
+        <v>-31.00624624047417</v>
       </c>
       <c r="F74">
-        <v>-4.494753620727038</v>
+        <v>-4.63197698718212</v>
       </c>
       <c r="G74">
-        <v>-20.51167949088988</v>
+        <v>-16.52874394459225</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.89523025355315</v>
       </c>
       <c r="E75">
-        <v>-35.00232567295875</v>
+        <v>-31.29560440837929</v>
       </c>
       <c r="F75">
-        <v>-4.7367248801352</v>
+        <v>-4.27289067532721</v>
       </c>
       <c r="G75">
-        <v>-20.44259999239468</v>
+        <v>-17.64282197164995</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.99176105661268</v>
       </c>
       <c r="E76">
-        <v>-35.46930870534074</v>
+        <v>-32.22503520642456</v>
       </c>
       <c r="F76">
-        <v>-4.903090810993241</v>
+        <v>-4.409634970742871</v>
       </c>
       <c r="G76">
-        <v>-20.29543465626469</v>
+        <v>-17.27162705305916</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.07927659991056</v>
       </c>
       <c r="E77">
-        <v>-34.74839602145265</v>
+        <v>-31.41620446391456</v>
       </c>
       <c r="F77">
-        <v>-5.163382380431207</v>
+        <v>-3.957378448029702</v>
       </c>
       <c r="G77">
-        <v>-19.64948101064209</v>
+        <v>-17.9251287425113</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.15565766087369</v>
       </c>
       <c r="E78">
-        <v>-35.27635948482192</v>
+        <v>-31.19892375255253</v>
       </c>
       <c r="F78">
-        <v>-5.093788799536093</v>
+        <v>-4.782775880744349</v>
       </c>
       <c r="G78">
-        <v>-19.70590925935897</v>
+        <v>-17.11578643234351</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.21747261737444</v>
       </c>
       <c r="E79">
-        <v>-34.75664916533163</v>
+        <v>-32.26819835642868</v>
       </c>
       <c r="F79">
-        <v>-5.006024568820186</v>
+        <v>-4.897506663935402</v>
       </c>
       <c r="G79">
-        <v>-20.43078134481948</v>
+        <v>-17.29726722826082</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.25803764496095</v>
       </c>
       <c r="E80">
-        <v>-35.90392220551588</v>
+        <v>-32.03724618203749</v>
       </c>
       <c r="F80">
-        <v>-5.380084028252617</v>
+        <v>-4.431469524199035</v>
       </c>
       <c r="G80">
-        <v>-19.58708219304514</v>
+        <v>-16.88235324527842</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.27584058043484</v>
       </c>
       <c r="E81">
-        <v>-35.92604380104336</v>
+        <v>-33.5063691911319</v>
       </c>
       <c r="F81">
-        <v>-5.322629553199348</v>
+        <v>-4.946368742544455</v>
       </c>
       <c r="G81">
-        <v>-19.71243434461687</v>
+        <v>-16.85413746564721</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.2688100354253</v>
       </c>
       <c r="E82">
-        <v>-37.51800619606983</v>
+        <v>-33.74165737938543</v>
       </c>
       <c r="F82">
-        <v>-5.197901626417083</v>
+        <v>-5.131461995852567</v>
       </c>
       <c r="G82">
-        <v>-19.91279683701741</v>
+        <v>-16.2850381347188</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.2337902543098</v>
       </c>
       <c r="E83">
-        <v>-36.95981743293637</v>
+        <v>-32.42792442739022</v>
       </c>
       <c r="F83">
-        <v>-5.29196187999982</v>
+        <v>-4.865453248059865</v>
       </c>
       <c r="G83">
-        <v>-19.78828721928543</v>
+        <v>-16.40276444464082</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.16804311656674</v>
       </c>
       <c r="E84">
-        <v>-37.32488489353872</v>
+        <v>-34.85372379839706</v>
       </c>
       <c r="F84">
-        <v>-5.36974163677184</v>
+        <v>-4.997048915544433</v>
       </c>
       <c r="G84">
-        <v>-19.98706892619096</v>
+        <v>-16.73336545382906</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.06799246664369</v>
       </c>
       <c r="E85">
-        <v>-37.78762474577551</v>
+        <v>-34.46495656907555</v>
       </c>
       <c r="F85">
-        <v>-5.045671854560254</v>
+        <v>-4.73270701822773</v>
       </c>
       <c r="G85">
-        <v>-19.66357234773</v>
+        <v>-15.95238293202345</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.93127892718479</v>
       </c>
       <c r="E86">
-        <v>-39.01026970734343</v>
+        <v>-34.73434643084385</v>
       </c>
       <c r="F86">
-        <v>-5.281854668847486</v>
+        <v>-5.399632502219844</v>
       </c>
       <c r="G86">
-        <v>-20.2086917420447</v>
+        <v>-16.45496181615851</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.75934541749253</v>
       </c>
       <c r="E87">
-        <v>-39.59227824375724</v>
+        <v>-35.74425500471644</v>
       </c>
       <c r="F87">
-        <v>-5.23230605372409</v>
+        <v>-4.753668949724487</v>
       </c>
       <c r="G87">
-        <v>-19.76678522600786</v>
+        <v>-16.56772727358994</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.55175974296975</v>
       </c>
       <c r="E88">
-        <v>-39.93943558965926</v>
+        <v>-36.62541679831396</v>
       </c>
       <c r="F88">
-        <v>-5.322852855733425</v>
+        <v>-4.948667491680715</v>
       </c>
       <c r="G88">
-        <v>-19.48501145297833</v>
+        <v>-15.9036500464126</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.30869645151016</v>
       </c>
       <c r="E89">
-        <v>-40.91869092297393</v>
+        <v>-37.58241015340692</v>
       </c>
       <c r="F89">
-        <v>-5.321641320708113</v>
+        <v>-5.000603543471636</v>
       </c>
       <c r="G89">
-        <v>-19.33819537940273</v>
+        <v>-15.47339830594676</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.03585898056476</v>
       </c>
       <c r="E90">
-        <v>-41.8586889151161</v>
+        <v>-38.86398414723666</v>
       </c>
       <c r="F90">
-        <v>-5.594182855402003</v>
+        <v>-5.306238196974549</v>
       </c>
       <c r="G90">
-        <v>-19.13896012775831</v>
+        <v>-16.67967502627316</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.73623531901417</v>
       </c>
       <c r="E91">
-        <v>-42.59430555410709</v>
+        <v>-39.22140301524006</v>
       </c>
       <c r="F91">
-        <v>-5.382183230443532</v>
+        <v>-5.46015144821949</v>
       </c>
       <c r="G91">
-        <v>-19.37658115493058</v>
+        <v>-16.32086651381756</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.41327509517948</v>
       </c>
       <c r="E92">
-        <v>-43.26346457279853</v>
+        <v>-41.1909608942111</v>
       </c>
       <c r="F92">
-        <v>-5.449797178944347</v>
+        <v>-4.929850689846421</v>
       </c>
       <c r="G92">
-        <v>-19.77966821397393</v>
+        <v>-15.5149903448294</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.07124187359933</v>
       </c>
       <c r="E93">
-        <v>-44.20533056046886</v>
+        <v>-42.2445624495467</v>
       </c>
       <c r="F93">
-        <v>-5.360495961637504</v>
+        <v>-5.360744603466228</v>
       </c>
       <c r="G93">
-        <v>-19.94181211339636</v>
+        <v>-16.77411826941749</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.712469403763624</v>
       </c>
       <c r="E94">
-        <v>-45.33660676622102</v>
+        <v>-42.77491694719202</v>
       </c>
       <c r="F94">
-        <v>-5.589700175808352</v>
+        <v>-5.149425180198439</v>
       </c>
       <c r="G94">
-        <v>-19.50046507955565</v>
+        <v>-16.35164631096894</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.344980121875416</v>
       </c>
       <c r="E95">
-        <v>-46.20360575735955</v>
+        <v>-43.54660741012811</v>
       </c>
       <c r="F95">
-        <v>-5.542390920849387</v>
+        <v>-5.596397668124745</v>
       </c>
       <c r="G95">
-        <v>-19.84915987538878</v>
+        <v>-16.39822734197925</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.97491576109215</v>
       </c>
       <c r="E96">
-        <v>-48.10498066743411</v>
+        <v>-45.25296132282534</v>
       </c>
       <c r="F96">
-        <v>-5.859490021474166</v>
+        <v>-5.337226570621953</v>
       </c>
       <c r="G96">
-        <v>-20.192910371459</v>
+        <v>-17.52290077003539</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.606715334293938</v>
       </c>
       <c r="E97">
-        <v>-48.24352932969879</v>
+        <v>-46.9422066607216</v>
       </c>
       <c r="F97">
-        <v>-5.745038762377187</v>
+        <v>-5.830751302079643</v>
       </c>
       <c r="G97">
-        <v>-20.04237324469726</v>
+        <v>-15.9274015553841</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.24965496762797</v>
       </c>
       <c r="E98">
-        <v>-50.71402926763534</v>
+        <v>-48.01242545142834</v>
       </c>
       <c r="F98">
-        <v>-5.881265977811458</v>
+        <v>-5.707292715588604</v>
       </c>
       <c r="G98">
-        <v>-20.04236496833341</v>
+        <v>-16.03118384749472</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.912281343811862</v>
       </c>
       <c r="E99">
-        <v>-52.01352696158743</v>
+        <v>-50.08444231905994</v>
       </c>
       <c r="F99">
-        <v>-5.657984031911397</v>
+        <v>-5.501178141811906</v>
       </c>
       <c r="G99">
-        <v>-19.81760706585398</v>
+        <v>-17.18249226968706</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.597166489482319</v>
       </c>
       <c r="E100">
-        <v>-52.80933607708838</v>
+        <v>-51.02125000126371</v>
       </c>
       <c r="F100">
-        <v>-5.524252736999859</v>
+        <v>-5.940330289927772</v>
       </c>
       <c r="G100">
-        <v>-19.67340466798164</v>
+        <v>-17.07493761093444</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.312544583304255</v>
       </c>
       <c r="E101">
-        <v>-54.45738928329236</v>
+        <v>-53.25020000351262</v>
       </c>
       <c r="F101">
-        <v>-5.705519756816269</v>
+        <v>-5.45866830762968</v>
       </c>
       <c r="G101">
-        <v>-20.46318496455787</v>
+        <v>-17.30300109313484</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.053130847205519</v>
       </c>
       <c r="E102">
-        <v>-55.77334571602534</v>
+        <v>-54.3643631059898</v>
       </c>
       <c r="F102">
-        <v>-5.610960635870168</v>
+        <v>-6.016144667658732</v>
       </c>
       <c r="G102">
-        <v>-20.13935402099744</v>
+        <v>-17.13694081833945</v>
       </c>
     </row>
   </sheetData>
